--- a/web/files/港岛-北角-101 Kings Road.xlsx
+++ b/web/files/港岛-北角-101 Kings Road.xlsx
@@ -764,7 +764,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2024-12-29</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2025-02-16</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2024-12-15</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6252,7 +6252,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6748,7 +6748,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -7802,7 +7802,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8732,7 +8732,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -8794,7 +8794,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2024-12-15</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9724,7 +9724,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -9848,7 +9848,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -9910,7 +9910,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -9972,7 +9972,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10034,7 +10034,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10220,7 +10220,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2024-12-22</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10282,7 +10282,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10468,7 +10468,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2024-12-15</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10530,7 +10530,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10592,7 +10592,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -10778,7 +10778,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -10902,7 +10902,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -10964,7 +10964,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11150,7 +11150,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11398,7 +11398,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11460,7 +11460,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -11584,7 +11584,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -11708,7 +11708,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12018,7 +12018,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12080,7 +12080,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -12390,7 +12390,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -12576,7 +12576,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -12762,7 +12762,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -12886,7 +12886,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -12948,7 +12948,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -13010,7 +13010,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13072,7 +13072,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13196,7 +13196,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -13258,7 +13258,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2024-12-15</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -13382,7 +13382,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -13444,7 +13444,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -13506,7 +13506,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -13568,7 +13568,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -13630,7 +13630,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -13692,7 +13692,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -13754,7 +13754,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -13816,7 +13816,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -14002,7 +14002,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -14064,7 +14064,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -14126,7 +14126,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -14188,7 +14188,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -14250,7 +14250,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -14312,7 +14312,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -14374,7 +14374,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -14498,7 +14498,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -14560,7 +14560,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -14622,7 +14622,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -14684,7 +14684,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -14746,7 +14746,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -14808,7 +14808,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -14870,7 +14870,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -14932,7 +14932,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -15056,7 +15056,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -15118,7 +15118,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -15180,7 +15180,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -15242,7 +15242,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2024-12-08</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -15304,7 +15304,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -15366,7 +15366,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -15428,7 +15428,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -15490,7 +15490,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -15552,7 +15552,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -15614,7 +15614,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -15676,7 +15676,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -15800,7 +15800,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -15862,7 +15862,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -15924,7 +15924,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -15986,7 +15986,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -16048,7 +16048,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -16320,7 +16320,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -16535,7 +16535,7 @@
           <t>B | 877呎 (3房)
 $4210万
 $48,000/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -16551,7 +16551,7 @@
           <t>D | 861呎 (3房)
 $4133万
 $48,000/呎
-(26年-06月-16日)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr"/>
@@ -16590,7 +16590,7 @@
           <t>D | 440呎 (2房)
 $1471万
 $33,441/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr">
@@ -16598,7 +16598,7 @@
           <t>E | 399呎 (2房)
 $972万
 $24,353/呎
-(25年-09月-28日)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="G6" s="21" t="inlineStr">
@@ -16606,7 +16606,7 @@
           <t>F | 262呎 (1房)
 $655万
 $25,011/呎
-(24年-12月-17日)</t>
+(24年-12月-18日)</t>
         </is>
       </c>
       <c r="H6" s="21" t="inlineStr">
@@ -16614,7 +16614,7 @@
           <t>G | 380呎 (2房)
 $967万
 $25,458/呎
-(24年-12月-05日)</t>
+(24年-12月-06日)</t>
         </is>
       </c>
       <c r="I6" s="21" t="inlineStr">
@@ -16622,7 +16622,7 @@
           <t>H | 432呎 (2房)
 $1050万
 $24,294/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr">
@@ -16630,7 +16630,7 @@
           <t>J | 244呎 (1房)
 $648万
 $26,541/呎
-(25年-07月-23日)</t>
+(25年-07月-24日)</t>
         </is>
       </c>
       <c r="K6" s="21" t="inlineStr">
@@ -16638,7 +16638,7 @@
           <t>K | 376呎 (2房)
 $1064万
 $28,298/呎
-(26年-02月-10日)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="L6" s="21" t="inlineStr">
@@ -16646,7 +16646,7 @@
           <t>L | 434呎 (2房)
 $1187万
 $27,357/呎
-(25年-02月-12日)</t>
+(25年-02月-13日)</t>
         </is>
       </c>
     </row>
@@ -16661,7 +16661,7 @@
           <t>A | 838呎 (3房)
 $3101万
 $37,000/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr"/>
@@ -16670,7 +16670,7 @@
           <t>C | 568呎 (3房)
 $1913万
 $33,680/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
@@ -16678,7 +16678,7 @@
           <t>D | 440呎 (2房)
 $1459万
 $33,150/呎
-(26年-03月-09日)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
@@ -16686,7 +16686,7 @@
           <t>E | 399呎 (2房)
 $956万
 $23,950/呎
-(25年-10月-27日)</t>
+(25年-10月-28日)</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -16694,7 +16694,7 @@
           <t>F | 262呎 (1房)
 $646万
 $24,668/呎
-(24年-12月-30日)</t>
+(24年-12月-31日)</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -16702,7 +16702,7 @@
           <t>G | 380呎 (2房)
 $928万
 $24,416/呎
-(25年-08月-06日)</t>
+(25年-08月-07日)</t>
         </is>
       </c>
       <c r="I7" s="21" t="inlineStr">
@@ -16710,7 +16710,7 @@
           <t>H | 432呎 (2房)
 $1037万
 $23,998/呎
-(24年-12月-12日)</t>
+(24年-12月-13日)</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
@@ -16718,7 +16718,7 @@
           <t>J | 244呎 (1房)
 $640万
 $26,213/呎
-(25年-01月-19日)</t>
+(25年-01月-20日)</t>
         </is>
       </c>
       <c r="K7" s="21" t="inlineStr">
@@ -16726,7 +16726,7 @@
           <t>K | 376呎 (2房)
 $1054万
 $28,021/呎
-(26年-02月-04日)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="L7" s="21" t="inlineStr">
@@ -16734,7 +16734,7 @@
           <t>L | 434呎 (2房)
 $1226万
 $28,256/呎
-(25年-11月-25日)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
     </row>
@@ -16749,7 +16749,7 @@
           <t>A | 838呎 (3房)
 $3017万
 $36,000/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr"/>
@@ -16758,7 +16758,7 @@
           <t>C | 568呎 (3房)
 $1851万
 $32,590/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -16766,7 +16766,7 @@
           <t>D | 440呎 (2房)
 $1446万
 $32,859/呎
-(26年-05月-03日)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr">
@@ -16774,7 +16774,7 @@
           <t>E | 399呎 (2房)
 $940万
 $23,549/呎
-(25年-11月-06日)</t>
+(25年-11月-07日)</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr">
@@ -16782,7 +16782,7 @@
           <t>F | 262呎 (1房)
 $644万
 $24,565/呎
-(25年-01月-02日)</t>
+(25年-01月-03日)</t>
         </is>
       </c>
       <c r="H8" s="21" t="inlineStr">
@@ -16790,7 +16790,7 @@
           <t>G | 380呎 (2房)
 $924万
 $24,326/呎
-(25年-09月-16日)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="I8" s="21" t="inlineStr">
@@ -16798,7 +16798,7 @@
           <t>H | 432呎 (2房)
 $1034万
 $23,942/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr">
@@ -16806,7 +16806,7 @@
           <t>J | 244呎 (1房)
 $632万
 $25,881/呎
-(24年-12月-17日)</t>
+(24年-12月-18日)</t>
         </is>
       </c>
       <c r="K8" s="21" t="inlineStr">
@@ -16814,7 +16814,7 @@
           <t>K | 376呎 (2房)
 $1043万
 $27,745/呎
-(25年-12月-17日)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="L8" s="21" t="inlineStr">
@@ -16822,7 +16822,7 @@
           <t>L | 434呎 (2房)
 $1164万
 $26,832/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -16837,7 +16837,7 @@
           <t>A | 838呎 (3房)
 $2944万
 $35,135/呎
-(25年-04月-08日)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr"/>
@@ -16846,7 +16846,7 @@
           <t>C | 568呎 (3房)
 $1750万
 $30,817/呎
-(25年-04月-08日)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -16854,7 +16854,7 @@
           <t>D | 440呎 (2房)
 $1433万
 $32,570/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -16862,7 +16862,7 @@
           <t>E | 399呎 (2房)
 $926万
 $23,216/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr">
@@ -16870,7 +16870,7 @@
           <t>F | 262呎 (1房)
 $634万
 $24,214/呎
-(24年-12月-29日)</t>
+(24年-12月-30日)</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -16878,7 +16878,7 @@
           <t>G | 380呎 (2房)
 $912万
 $23,989/呎
-(25年-09月-29日)</t>
+(25年-09月-30日)</t>
         </is>
       </c>
       <c r="I9" s="21" t="inlineStr">
@@ -16886,7 +16886,7 @@
           <t>H | 432呎 (2房)
 $1017万
 $23,535/呎
-(25年-05月-05日)</t>
+(25年-05月-06日)</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr">
@@ -16894,7 +16894,7 @@
           <t>J | 244呎 (1房)
 $642万
 $26,311/呎
-(24年-12月-18日)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
       <c r="K9" s="21" t="inlineStr">
@@ -16902,7 +16902,7 @@
           <t>K | 376呎 (2房)
 $1033万
 $27,471/呎
-(26年-01月-12日)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
@@ -16910,7 +16910,7 @@
           <t>L | 434呎 (2房)
 $1153万
 $26,567/呎
-(25年-10月-21日)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
     </row>
@@ -16925,7 +16925,7 @@
           <t>A | 838呎 (3房)
 $2933万
 $35,000/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr"/>
@@ -16934,7 +16934,7 @@
           <t>C | 568呎 (3房)
 $1743万
 $30,680/呎
-(25年-11月-03日)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -16942,7 +16942,7 @@
           <t>D | 440呎 (2房)
 $1480万
 $33,627/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -16950,7 +16950,7 @@
           <t>E | 399呎 (2房)
 $912万
 $22,852/呎
-(25年-10月-22日)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -16958,7 +16958,7 @@
           <t>F | 262呎 (1房)
 $625万
 $23,863/呎
-(24年-12月-18日)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -16966,7 +16966,7 @@
           <t>G | 380呎 (2房)
 $899万
 $23,653/呎
-(25年-10月-26日)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="I10" s="21" t="inlineStr">
@@ -16974,7 +16974,7 @@
           <t>H | 432呎 (2房)
 $1028万
 $23,789/呎
-(25年-02月-16日)</t>
+(25年-02月-17日)</t>
         </is>
       </c>
       <c r="J10" s="21" t="inlineStr">
@@ -16982,7 +16982,7 @@
           <t>J | 244呎 (1房)
 $634万
 $25,996/呎
-(24年-12月-18日)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
       <c r="K10" s="21" t="inlineStr">
@@ -16990,7 +16990,7 @@
           <t>K | 376呎 (2房)
 $1008万
 $26,822/呎
-(24年-12月-08日)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
       <c r="L10" s="21" t="inlineStr">
@@ -16998,7 +16998,7 @@
           <t>L | 434呎 (2房)
 $1142万
 $26,304/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
     </row>
@@ -17013,7 +17013,7 @@
           <t>A | 838呎 (3房)
 $2430万
 $29,000/呎
-(24年-12月-12日)</t>
+(24年-12月-13日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr"/>
@@ -17022,7 +17022,7 @@
           <t>C | 568呎 (3房)
 $1704万
 $30,000/呎
-(26年-02月-02日)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -17030,7 +17030,7 @@
           <t>D | 440呎 (2房)
 $1409万
 $32,030/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -17038,7 +17038,7 @@
           <t>E | 399呎 (2房)
 $898万
 $22,514/呎
-(25年-10月-26日)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -17046,7 +17046,7 @@
           <t>F | 262呎 (1房)
 $599万
 $22,863/呎
-(24年-12月-17日)</t>
+(24年-12月-18日)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -17054,7 +17054,7 @@
           <t>G | 380呎 (2房)
 $886万
 $23,316/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="I11" s="21" t="inlineStr">
@@ -17062,7 +17062,7 @@
           <t>H | 432呎 (2房)
 $1010万
 $23,368/呎
-(24年-12月-15日)</t>
+(24年-12月-16日)</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
@@ -17070,7 +17070,7 @@
           <t>J | 244呎 (1房)
 $627万
 $25,684/呎
-(24年-12月-17日)</t>
+(24年-12月-18日)</t>
         </is>
       </c>
       <c r="K11" s="21" t="inlineStr">
@@ -17078,7 +17078,7 @@
           <t>K | 376呎 (2房)
 $1012万
 $26,918/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
@@ -17086,7 +17086,7 @@
           <t>L | 434呎 (2房)
 $1130万
 $26,041/呎
-(25年-08月-06日)</t>
+(25年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -17101,7 +17101,7 @@
           <t>A | 549呎 (3房)
 $1653万
 $30,104/呎
-(26年-02月-04日)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -17109,7 +17109,7 @@
           <t>B | 310呎 (1房)
 $866万
 $27,948/呎
-(26年-01月-26日)</t>
+(26年-01月-27日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -17117,7 +17117,7 @@
           <t>C | 568呎 (3房)
 $1669万
 $29,380/呎
-(25年-12月-21日)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -17125,7 +17125,7 @@
           <t>D | 440呎 (2房)
 $1512万
 $34,368/呎
-(26年-07月-14日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -17133,7 +17133,7 @@
           <t>E | 399呎 (2房)
 $885万
 $22,175/呎
-(25年-07月-15日)</t>
+(25年-07月-16日)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -17141,7 +17141,7 @@
           <t>F | 262呎 (1房)
 $607万
 $23,168/呎
-(24年-12月-18日)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -17149,7 +17149,7 @@
           <t>G | 380呎 (2房)
 $898万
 $23,634/呎
-(25年-07月-10日)</t>
+(25年-07月-11日)</t>
         </is>
       </c>
       <c r="I12" s="21" t="inlineStr">
@@ -17157,7 +17157,7 @@
           <t>H | 432呎 (2房)
 $964万
 $22,312/呎
-(24年-12月-12日)</t>
+(24年-12月-13日)</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr">
@@ -17165,7 +17165,7 @@
           <t>J | 244呎 (1房)
 $619万
 $25,373/呎
-(24年-12月-18日)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
       <c r="K12" s="21" t="inlineStr">
@@ -17173,7 +17173,7 @@
           <t>K | 376呎 (2房)
 $1002万
 $26,644/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
@@ -17181,7 +17181,7 @@
           <t>L | 434呎 (2房)
 $1119万
 $25,779/呎
-(25年-04月-22日)</t>
+(25年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -17196,7 +17196,7 @@
           <t>A | 549呎 (3房)
 $1637万
 $29,816/呎
-(26年-03月-04日)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -17204,7 +17204,7 @@
           <t>B | 310呎 (1房)
 $857万
 $27,635/呎
-(26年-01月-18日)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -17212,7 +17212,7 @@
           <t>C | 568呎 (3房)
 $1636万
 $28,799/呎
-(26年-01月-11日)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -17228,7 +17228,7 @@
           <t>E | 399呎 (2房)
 $903万
 $22,637/呎
-(25年-07月-06日)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
@@ -17236,7 +17236,7 @@
           <t>F | 262呎 (1房)
 $584万
 $22,305/呎
-(24年-12月-18日)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -17244,7 +17244,7 @@
           <t>G | 380呎 (2房)
 $888万
 $23,361/呎
-(24年-12月-09日)</t>
+(24年-12月-10日)</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
@@ -17252,7 +17252,7 @@
           <t>H | 432呎 (2房)
 $956万
 $22,125/呎
-(24年-12月-08日)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr">
@@ -17260,7 +17260,7 @@
           <t>J | 244呎 (1房)
 $594万
 $24,352/呎
-(24年-12月-19日)</t>
+(24年-12月-20日)</t>
         </is>
       </c>
       <c r="K13" s="21" t="inlineStr">
@@ -17268,7 +17268,7 @@
           <t>K | 376呎 (2房)
 $951万
 $25,293/呎
-(25年-11月-13日)</t>
+(25年-11月-14日)</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -17276,7 +17276,7 @@
           <t>L | 434呎 (2房)
 $1108万
 $25,535/呎
-(25年-04月-21日)</t>
+(25年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -17291,7 +17291,7 @@
           <t>A | 549呎 (3房)
 $1584万
 $28,852/呎
-(25年-02月-20日)</t>
+(25年-02月-21日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -17299,7 +17299,7 @@
           <t>B | 310呎 (1房)
 $847万
 $27,323/呎
-(26年-01月-15日)</t>
+(26年-01月-16日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -17307,7 +17307,7 @@
           <t>C | 568呎 (3房)
 $1590万
 $28,000/呎
-(24年-12月-05日)</t>
+(24年-12月-06日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -17315,7 +17315,7 @@
           <t>D | 440呎 (2房)
 $1422万
 $32,318/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -17323,7 +17323,7 @@
           <t>E | 399呎 (2房)
 $871万
 $21,840/呎
-(25年-03月-12日)</t>
+(25年-03月-13日)</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -17331,7 +17331,7 @@
           <t>F | 262呎 (1房)
 $595万
 $22,718/呎
-(25年-01月-01日)</t>
+(25年-01月-02日)</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr">
@@ -17339,7 +17339,7 @@
           <t>G | 380呎 (2房)
 $877万
 $23,084/呎
-(24年-12月-05日)</t>
+(24年-12月-06日)</t>
         </is>
       </c>
       <c r="I14" s="21" t="inlineStr">
@@ -17347,7 +17347,7 @@
           <t>H | 432呎 (2房)
 $975万
 $22,565/呎
-(24年-12月-08日)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
       <c r="J14" s="21" t="inlineStr">
@@ -17355,7 +17355,7 @@
           <t>J | 244呎 (1房)
 $605万
 $24,795/呎
-(24年-12月-18日)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
       <c r="K14" s="21" t="inlineStr">
@@ -17363,7 +17363,7 @@
           <t>K | 376呎 (2房)
 $941万
 $25,037/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="L14" s="21" t="inlineStr">
@@ -17371,7 +17371,7 @@
           <t>L | 434呎 (2房)
 $1129万
 $26,012/呎
-(24年-12月-11日)</t>
+(24年-12月-12日)</t>
         </is>
       </c>
     </row>
@@ -17386,7 +17386,7 @@
           <t>A | 549呎 (3房)
 $1618万
 $29,466/呎
-(26年-02月-22日)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -17394,7 +17394,7 @@
           <t>B | 310呎 (1房)
 $837万
 $27,010/呎
-(26年-01月-06日)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -17402,7 +17402,7 @@
           <t>C | 568呎 (3房)
 $1565万
 $27,560/呎
-(25年-08月-11日)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -17410,7 +17410,7 @@
           <t>D | 440呎 (2房)
 $1343万
 $30,530/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -17418,7 +17418,7 @@
           <t>E | 399呎 (2房)
 $889万
 $22,291/呎
-(24年-12月-09日)</t>
+(24年-12月-10日)</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -17426,7 +17426,7 @@
           <t>F | 262呎 (1房)
 $573万
 $21,870/呎
-(24年-12月-18日)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -17434,7 +17434,7 @@
           <t>G | 380呎 (2房)
 $867万
 $22,808/呎
-(24年-12月-09日)</t>
+(24年-12月-10日)</t>
         </is>
       </c>
       <c r="I15" s="21" t="inlineStr">
@@ -17442,7 +17442,7 @@
           <t>H | 432呎 (2房)
 $966万
 $22,373/呎
-(24年-12月-09日)</t>
+(24年-12月-10日)</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr">
@@ -17450,7 +17450,7 @@
           <t>J | 244呎 (1房)
 $599万
 $24,541/呎
-(24年-12月-19日)</t>
+(24年-12月-20日)</t>
         </is>
       </c>
       <c r="K15" s="21" t="inlineStr">
@@ -17458,7 +17458,7 @@
           <t>K | 376呎 (2房)
 $958万
 $25,489/呎
-(25年-02月-05日)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr">
@@ -17466,7 +17466,7 @@
           <t>L | 434呎 (2房)
 $1087万
 $25,041/呎
-(24年-12月-09日)</t>
+(24年-12月-10日)</t>
         </is>
       </c>
     </row>
@@ -17481,7 +17481,7 @@
           <t>A | 549呎 (3房)
 $1583万
 $28,842/呎
-(26年-01月-04日)</t>
+(26年-01月-05日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -17489,7 +17489,7 @@
           <t>B | 310呎 (1房)
 $828万
 $26,697/呎
-(26年-01月-06日)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -17497,7 +17497,7 @@
           <t>C | 568呎 (3房)
 $1535万
 $27,019/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -17505,7 +17505,7 @@
           <t>D | 440呎 (2房)
 $1321万
 $30,020/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -17513,7 +17513,7 @@
           <t>E | 399呎 (2房)
 $858万
 $21,504/呎
-(24年-12月-08日)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -17521,7 +17521,7 @@
           <t>F | 262呎 (1房)
 $584万
 $22,271/呎
-(24年-12月-18日)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
@@ -17529,7 +17529,7 @@
           <t>G | 380呎 (2房)
 $856万
 $22,532/呎
-(24年-12月-08日)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
       <c r="I16" s="21" t="inlineStr">
@@ -17537,7 +17537,7 @@
           <t>H | 432呎 (2房)
 $958万
 $22,178/呎
-(24年-12月-12日)</t>
+(24年-12月-13日)</t>
         </is>
       </c>
       <c r="J16" s="21" t="inlineStr">
@@ -17545,7 +17545,7 @@
           <t>J | 244呎 (1房)
 $593万
 $24,287/呎
-(24年-12月-18日)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
       <c r="K16" s="21" t="inlineStr">
@@ -17553,7 +17553,7 @@
           <t>K | 376呎 (2房)
 $948万
 $25,226/呎
-(24年-12月-08日)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
       <c r="L16" s="21" t="inlineStr">
@@ -17561,7 +17561,7 @@
           <t>L | 434呎 (2房)
 $1107万
 $25,505/呎
-(24年-12月-10日)</t>
+(24年-12月-11日)</t>
         </is>
       </c>
     </row>
@@ -17576,7 +17576,7 @@
           <t>A | 549呎 (3房)
 $1546万
 $28,157/呎
-(25年-12月-23日)</t>
+(25年-12月-24日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -17584,7 +17584,7 @@
           <t>B | 310呎 (1房)
 $784万
 $25,300/呎
-(25年-11月-16日)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -17592,7 +17592,7 @@
           <t>C | 568呎 (3房)
 $1592万
 $28,032/呎
-(25年-12月-04日)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -17600,7 +17600,7 @@
           <t>D | 440呎 (2房)
 $1298万
 $29,509/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -17608,7 +17608,7 @@
           <t>E | 399呎 (2房)
 $851万
 $21,336/呎
-(24年-12月-05日)</t>
+(24年-12月-06日)</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -17616,7 +17616,7 @@
           <t>F | 262呎 (1房)
 $578万
 $22,050/呎
-(24年-12月-17日)</t>
+(24年-12月-18日)</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">
@@ -17624,7 +17624,7 @@
           <t>G | 380呎 (2房)
 $846万
 $22,255/呎
-(24年-12月-11日)</t>
+(24年-12月-12日)</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr">
@@ -17632,7 +17632,7 @@
           <t>H | 432呎 (2房)
 $923万
 $21,375/呎
-(24年-12月-05日)</t>
+(24年-12月-06日)</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr">
@@ -17640,7 +17640,7 @@
           <t>J | 244呎 (1房)
 $592万
 $24,275/呎
-(24年-12月-17日)</t>
+(24年-12月-18日)</t>
         </is>
       </c>
       <c r="K17" s="21" t="inlineStr">
@@ -17648,7 +17648,7 @@
           <t>K | 376呎 (2房)
 $913万
 $24,271/呎
-(24年-12月-05日)</t>
+(24年-12月-06日)</t>
         </is>
       </c>
       <c r="L17" s="21" t="inlineStr">
@@ -17656,7 +17656,7 @@
           <t>L | 434呎 (2房)
 $1096万
 $25,249/呎
-(24年-12月-08日)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
     </row>
@@ -17671,7 +17671,7 @@
           <t>A | 549呎 (3房)
 $1452万
 $26,455/呎
-(25年-09月-22日)</t>
+(25年-09月-23日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -17679,7 +17679,7 @@
           <t>B | 310呎 (1房)
 $808万
 $26,071/呎
-(25年-12月-11日)</t>
+(25年-12月-12日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -17687,7 +17687,7 @@
           <t>C | 568呎 (3房)
 $1500万
 $26,400/呎
-(25年-08月-11日)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -17695,7 +17695,7 @@
           <t>D | 440呎 (2房)
 $1285万
 $29,200/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -17703,7 +17703,7 @@
           <t>E | 399呎 (2房)
 $845万
 $21,168/呎
-(24年-12月-15日)</t>
+(24年-12月-16日)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -17711,7 +17711,7 @@
           <t>F | 262呎 (1房)
 $572万
 $21,824/呎
-(24年-12月-18日)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
@@ -17719,7 +17719,7 @@
           <t>G | 380呎 (2房)
 $835万
 $21,979/呎
-(24年-12月-09日)</t>
+(24年-12月-10日)</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -17727,7 +17727,7 @@
           <t>H | 432呎 (2房)
 $1255万
 $29,058/呎
-(26年-03月-31日)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="J18" s="21" t="inlineStr">
@@ -17735,7 +17735,7 @@
           <t>J | 244呎 (1房)
 $586万
 $24,016/呎
-(24年-12月-18日)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
       <c r="K18" s="21" t="inlineStr">
@@ -17743,7 +17743,7 @@
           <t>K | 376呎 (2房)
 $903万
 $24,016/呎
-(25年-07月-30日)</t>
+(25年-07月-31日)</t>
         </is>
       </c>
       <c r="L18" s="21" t="inlineStr">
@@ -17751,7 +17751,7 @@
           <t>L | 434呎 (2房)
 $1055万
 $24,302/呎
-(24年-12月-09日)</t>
+(24年-12月-10日)</t>
         </is>
       </c>
     </row>
@@ -17766,7 +17766,7 @@
           <t>A | 549呎 (3房)
 $1439万
 $26,208/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -17774,7 +17774,7 @@
           <t>B | 310呎 (1房)
 $766万
 $24,700/呎
-(25年-10月-27日)</t>
+(25年-10月-28日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -17782,7 +17782,7 @@
           <t>C | 568呎 (3房)
 $1465万
 $25,799/呎
-(24年-12月-08日)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -17790,7 +17790,7 @@
           <t>D | 440呎 (2房)
 $1276万
 $28,991/呎
-(26年-04月-09日)</t>
+(26年-04月-10日)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -17798,7 +17798,7 @@
           <t>E | 399呎 (2房)
 $838万
 $21,000/呎
-(25年-05月-14日)</t>
+(25年-05月-15日)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -17806,7 +17806,7 @@
           <t>F | 262呎 (1房)
 $566万
 $21,599/呎
-(24年-12月-19日)</t>
+(24年-12月-20日)</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
@@ -17814,7 +17814,7 @@
           <t>G | 380呎 (2房)
 $802万
 $21,100/呎
-(24年-12月-08日)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">
@@ -17822,7 +17822,7 @@
           <t>H | 432呎 (2房)
 $907万
 $21,000/呎
-(24年-12月-08日)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
       <c r="J19" s="21" t="inlineStr">
@@ -17830,7 +17830,7 @@
           <t>J | 244呎 (1房)
 $580万
 $23,758/呎
-(24年-12月-19日)</t>
+(24年-12月-20日)</t>
         </is>
       </c>
       <c r="K19" s="21" t="inlineStr">
@@ -17838,7 +17838,7 @@
           <t>K | 376呎 (2房)
 $893万
 $23,761/呎
-(25年-07月-31日)</t>
+(25年-08月-01日)</t>
         </is>
       </c>
       <c r="L19" s="21" t="inlineStr">
@@ -17846,7 +17846,7 @@
           <t>L | 434呎 (2房)
 $1074万
 $24,747/呎
-(24年-12月-08日)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
     </row>
@@ -17861,7 +17861,7 @@
           <t>A | 549呎 (3房)
 $1414万
 $25,754/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -17869,7 +17869,7 @@
           <t>B | 310呎 (1房)
 $782万
 $25,213/呎
-(25年-01月-15日)</t>
+(25年-01月-16日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -17877,7 +17877,7 @@
           <t>C | 568呎 (3房)
 $1447万
 $25,474/呎
-(25年-02月-13日)</t>
+(25年-02月-14日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -17885,7 +17885,7 @@
           <t>D | 440呎 (2房)
 $1266万
 $28,780/呎
-(25年-12月-04日)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -17893,7 +17893,7 @@
           <t>E | 399呎 (2房)
 $852万
 $21,341/呎
-(25年-01月-13日)</t>
+(25年-01月-14日)</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -17901,7 +17901,7 @@
           <t>F | 262呎 (1房)
 $544万
 $20,763/呎
-(24年-12月-17日)</t>
+(24年-12月-18日)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -17909,7 +17909,7 @@
           <t>G | 380呎 (2房)
 $818万
 $21,518/呎
-(24年-12月-15日)</t>
+(24年-12月-16日)</t>
         </is>
       </c>
       <c r="I20" s="21" t="inlineStr">
@@ -17917,7 +17917,7 @@
           <t>H | 432呎 (2房)
 $925万
 $21,410/呎
-(24年-12月-05日)</t>
+(24年-12月-06日)</t>
         </is>
       </c>
       <c r="J20" s="21" t="inlineStr">
@@ -17925,7 +17925,7 @@
           <t>J | 244呎 (1房)
 $575万
 $23,574/呎
-(24年-12月-19日)</t>
+(24年-12月-20日)</t>
         </is>
       </c>
       <c r="K20" s="21" t="inlineStr">
@@ -17933,7 +17933,7 @@
           <t>K | 376呎 (2房)
 $912万
 $24,247/呎
-(24年-12月-08日)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
       <c r="L20" s="21" t="inlineStr">
@@ -17941,7 +17941,7 @@
           <t>L | 434呎 (2房)
 $1066万
 $24,553/呎
-(24年-12月-22日)</t>
+(24年-12月-23日)</t>
         </is>
       </c>
     </row>
@@ -17956,7 +17956,7 @@
           <t>A | 549呎 (3房)
 $1400万
 $25,508/呎
-(25年-04月-28日)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -17964,7 +17964,7 @@
           <t>B | 310呎 (1房)
 $753万
 $24,277/呎
-(25年-04月-28日)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -17972,7 +17972,7 @@
           <t>C | 568呎 (3房)
 $1445万
 $25,438/呎
-(25年-11月-02日)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -17980,7 +17980,7 @@
           <t>D | 440呎 (2房)
 $1257万
 $28,570/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -17988,7 +17988,7 @@
           <t>E | 399呎 (2房)
 $841万
 $21,078/呎
-(24年-12月-05日)</t>
+(24年-12月-06日)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -17996,7 +17996,7 @@
           <t>F | 262呎 (1房)
 $553万
 $21,115/呎
-(24年-12月-17日)</t>
+(24年-12月-18日)</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">
@@ -18004,7 +18004,7 @@
           <t>G | 380呎 (2房)
 $811万
 $21,334/呎
-(24年-12月-12日)</t>
+(24年-12月-13日)</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -18012,7 +18012,7 @@
           <t>H | 432呎 (2房)
 $917万
 $21,218/呎
-(24年-12月-05日)</t>
+(24年-12月-06日)</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -18020,7 +18020,7 @@
           <t>J | 244呎 (1房)
 $570万
 $23,381/呎
-(24年-12月-17日)</t>
+(24年-12月-18日)</t>
         </is>
       </c>
       <c r="K21" s="21" t="inlineStr">
@@ -18028,7 +18028,7 @@
           <t>K | 376呎 (2房)
 $914万
 $24,303/呎
-(24年-12月-05日)</t>
+(24年-12月-06日)</t>
         </is>
       </c>
       <c r="L21" s="21" t="inlineStr">
@@ -18036,7 +18036,7 @@
           <t>L | 434呎 (2房)
 $1068万
 $24,608/呎
-(24年-12月-05日)</t>
+(24年-12月-06日)</t>
         </is>
       </c>
     </row>
@@ -18051,7 +18051,7 @@
           <t>A | 549呎 (3房)
 $1446万
 $26,344/呎
-(26年-01月-04日)</t>
+(26年-01月-05日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -18059,7 +18059,7 @@
           <t>B | 310呎 (1房)
 $748万
 $24,129/呎
-(24年-12月-18日)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -18067,7 +18067,7 @@
           <t>C | 568呎 (3房)
 $1387万
 $24,417/呎
-(25年-07月-31日)</t>
+(25年-08月-01日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -18075,7 +18075,7 @@
           <t>D | 440呎 (2房)
 $1248万
 $28,359/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -18083,7 +18083,7 @@
           <t>E | 399呎 (2房)
 $808万
 $20,241/呎
-(25年-01月-09日)</t>
+(25年-01月-10日)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -18091,7 +18091,7 @@
           <t>F | 262呎 (1房)
 $547万
 $20,870/呎
-(24年-12月-18日)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
@@ -18099,7 +18099,7 @@
           <t>G | 380呎 (2房)
 $781万
 $20,563/呎
-(24年-12月-12日)</t>
+(24年-12月-13日)</t>
         </is>
       </c>
       <c r="I22" s="21" t="inlineStr">
@@ -18107,7 +18107,7 @@
           <t>H | 432呎 (2房)
 $908万
 $21,028/呎
-(24年-12月-08日)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
       <c r="J22" s="21" t="inlineStr">
@@ -18115,7 +18115,7 @@
           <t>J | 244呎 (1房)
 $566万
 $23,193/呎
-(24年-12月-18日)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
       <c r="K22" s="21" t="inlineStr">
@@ -18123,7 +18123,7 @@
           <t>K | 376呎 (2房)
 $881万
 $23,441/呎
-(25年-09月-16日)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="L22" s="21" t="inlineStr">
@@ -18131,7 +18131,7 @@
           <t>L | 434呎 (2房)
 $1060万
 $24,419/呎
-(24年-12月-08日)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
     </row>
@@ -18146,7 +18146,7 @@
           <t>A | 549呎 (3房)
 $1373万
 $25,016/呎
-(25年-06月-18日)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -18154,7 +18154,7 @@
           <t>B | 310呎 (1房)
 $744万
 $23,997/呎
-(25年-06月-18日)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -18162,7 +18162,7 @@
           <t>C | 568呎 (3房)
 $1373万
 $24,180/呎
-(25年-04月-13日)</t>
+(25年-04月-14日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -18170,7 +18170,7 @@
           <t>D | 440呎 (2房)
 $1239万
 $28,150/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -18178,7 +18178,7 @@
           <t>E | 399呎 (2房)
 $798万
 $19,987/呎
-(24年-12月-12日)</t>
+(24年-12月-13日)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -18186,7 +18186,7 @@
           <t>F | 262呎 (1房)
 $540万
 $20,626/呎
-(24年-12月-17日)</t>
+(24年-12月-18日)</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
@@ -18194,7 +18194,7 @@
           <t>G | 380呎 (2房)
 $797万
 $20,968/呎
-(24年-12月-05日)</t>
+(24年-12月-06日)</t>
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr">
@@ -18202,7 +18202,7 @@
           <t>H | 432呎 (2房)
 $1113万
 $25,759/呎
-(26年-03月-10日)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
@@ -18210,7 +18210,7 @@
           <t>J | 244呎 (1房)
 $562万
 $23,012/呎
-(24年-12月-17日)</t>
+(24年-12月-18日)</t>
         </is>
       </c>
       <c r="K23" s="21" t="inlineStr">
@@ -18218,7 +18218,7 @@
           <t>K | 376呎 (2房)
 $874万
 $23,255/呎
-(25年-08月-18日)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="L23" s="21" t="inlineStr">
@@ -18226,7 +18226,7 @@
           <t>L | 434呎 (2房)
 $1051万
 $24,226/呎
-(24年-12月-10日)</t>
+(24年-12月-11日)</t>
         </is>
       </c>
     </row>
@@ -18241,7 +18241,7 @@
           <t>A | 549呎 (3房)
 $1418万
 $25,832/呎
-(25年-12月-08日)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -18249,7 +18249,7 @@
           <t>B | 310呎 (1房)
 $735万
 $23,710/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -18257,7 +18257,7 @@
           <t>C | 568呎 (3房)
 $1632万
 $28,731/呎
-(26年-03月-19日)</t>
+(26年-03月-20日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -18265,7 +18265,7 @@
           <t>D | 440呎 (2房)
 $1229万
 $27,941/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -18273,7 +18273,7 @@
           <t>E | 399呎 (2房)
 $810万
 $20,298/呎
-(24年-12月-15日)</t>
+(24年-12月-16日)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -18281,7 +18281,7 @@
           <t>F | 262呎 (1房)
 $519万
 $19,817/呎
-(24年-12月-18日)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
@@ -18289,7 +18289,7 @@
           <t>G | 380呎 (2房)
 $768万
 $20,205/呎
-(24年-12月-09日)</t>
+(24年-12月-10日)</t>
         </is>
       </c>
       <c r="I24" s="21" t="inlineStr">
@@ -18297,7 +18297,7 @@
           <t>H | 432呎 (2房)
 $867万
 $20,074/呎
-(24年-12月-09日)</t>
+(24年-12月-10日)</t>
         </is>
       </c>
       <c r="J24" s="21" t="inlineStr">
@@ -18305,7 +18305,7 @@
           <t>J | 244呎 (1房)
 $557万
 $22,832/呎
-(24年-12月-18日)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
       <c r="K24" s="21" t="inlineStr">
@@ -18313,7 +18313,7 @@
           <t>K | 376呎 (2房)
 $867万
 $23,069/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
       <c r="L24" s="21" t="inlineStr">
@@ -18321,7 +18321,7 @@
           <t>L | 434呎 (2房)
 $1043万
 $24,035/呎
-(24年-12月-12日)</t>
+(24年-12月-13日)</t>
         </is>
       </c>
     </row>
@@ -18336,7 +18336,7 @@
           <t>A | 549呎 (3房)
 $1346万
 $24,525/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -18344,7 +18344,7 @@
           <t>B | 310呎 (1房)
 $727万
 $23,442/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -18352,7 +18352,7 @@
           <t>C | 568呎 (3房)
 $1346万
 $23,704/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -18360,7 +18360,7 @@
           <t>D | 440呎 (2房)
 $1220万
 $27,730/呎
-(26年-03月-09日)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -18368,7 +18368,7 @@
           <t>E | 399呎 (2房)
 $777万
 $19,481/呎
-(24年-12月-17日)</t>
+(24年-12月-18日)</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
@@ -18376,7 +18376,7 @@
           <t>F | 262呎 (1房)
 $528万
 $20,141/呎
-(24年-12月-18日)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
@@ -18384,7 +18384,7 @@
           <t>G | 380呎 (2房)
 $783万
 $20,597/呎
-(24年-12月-08日)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
       <c r="I25" s="21" t="inlineStr">
@@ -18392,7 +18392,7 @@
           <t>H | 432呎 (2房)
 $884万
 $20,456/呎
-(24年-12月-08日)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
       <c r="J25" s="21" t="inlineStr">
@@ -18400,7 +18400,7 @@
           <t>J | 244呎 (1房)
 $553万
 $22,652/呎
-(24年-12月-18日)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
       <c r="K25" s="21" t="inlineStr">
@@ -18408,7 +18408,7 @@
           <t>K | 376呎 (2房)
 $885万
 $23,537/呎
-(24年-12月-08日)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
       <c r="L25" s="21" t="inlineStr">
@@ -18416,7 +18416,7 @@
           <t>L | 434呎 (2房)
 $1035万
 $23,841/呎
-(24年-12月-08日)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
     </row>
@@ -18431,7 +18431,7 @@
           <t>A | 549呎 (3房)
 $1333万
 $24,279/呎
-(25年-06月-17日)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -18439,7 +18439,7 @@
           <t>B | 310呎 (1房)
 $718万
 $23,174/呎
-(25年-07月-21日)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -18447,7 +18447,7 @@
           <t>C | 568呎 (3房)
 $1333万
 $23,467/呎
-(25年-11月-06日)</t>
+(25年-11月-07日)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -18455,7 +18455,7 @@
           <t>D | 440呎 (2房)
 $1211万
 $27,520/呎
-(26年-02月-08日)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
@@ -18463,7 +18463,7 @@
           <t>E | 399呎 (2房)
 $789万
 $19,777/呎
-(24年-12月-08日)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -18471,7 +18471,7 @@
           <t>F | 262呎 (1房)
 $521万
 $19,897/呎
-(24年-12月-17日)</t>
+(24年-12月-18日)</t>
         </is>
       </c>
       <c r="H26" s="21" t="inlineStr">
@@ -18479,7 +18479,7 @@
           <t>G | 380呎 (2房)
 $776万
 $20,413/呎
-(24年-12月-05日)</t>
+(24年-12月-06日)</t>
         </is>
       </c>
       <c r="I26" s="21" t="inlineStr">
@@ -18487,7 +18487,7 @@
           <t>H | 432呎 (2房)
 $876万
 $20,266/呎
-(24年-12月-12日)</t>
+(24年-12月-13日)</t>
         </is>
       </c>
       <c r="J26" s="21" t="inlineStr">
@@ -18495,7 +18495,7 @@
           <t>J | 244呎 (1房)
 $533万
 $21,844/呎
-(24年-12月-17日)</t>
+(24年-12月-18日)</t>
         </is>
       </c>
       <c r="K26" s="21" t="inlineStr">
@@ -18503,7 +18503,7 @@
           <t>K | 376呎 (2房)
 $853万
 $22,697/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="L26" s="21" t="inlineStr">
@@ -18511,7 +18511,7 @@
           <t>L | 434呎 (2房)
 $1026万
 $23,650/呎
-(24年-12月-05日)</t>
+(24年-12月-06日)</t>
         </is>
       </c>
     </row>
@@ -18526,7 +18526,7 @@
           <t>A | 549呎 (3房)
 $1333万
 $24,286/呎
-(24年-12月-18日)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -18534,7 +18534,7 @@
           <t>B | 310呎 (1房)
 $710万
 $22,906/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -18542,7 +18542,7 @@
           <t>C | 568呎 (3房)
 $1328万
 $23,387/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -18550,7 +18550,7 @@
           <t>D | 440呎 (2房)
 $1174万
 $26,680/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -18558,7 +18558,7 @@
           <t>E | 399呎 (2房)
 $775万
 $19,434/呎
-(24年-12月-10日)</t>
+(24年-12月-11日)</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
@@ -18566,7 +18566,7 @@
           <t>F | 262呎 (1房)
 $502万
 $19,156/呎
-(24年-12月-17日)</t>
+(24年-12月-18日)</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -18574,7 +18574,7 @@
           <t>G | 380呎 (2房)
 $769万
 $20,229/呎
-(24年-12月-08日)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -18582,7 +18582,7 @@
           <t>H | 432呎 (2房)
 $863万
 $19,972/呎
-(24年-12月-08日)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
       <c r="J27" s="21" t="inlineStr">
@@ -18590,7 +18590,7 @@
           <t>J | 244呎 (1房)
 $544万
 $22,287/呎
-(24年-12月-17日)</t>
+(24年-12月-18日)</t>
         </is>
       </c>
       <c r="K27" s="21" t="inlineStr">
@@ -18598,7 +18598,7 @@
           <t>K | 376呎 (2房)
 $846万
 $22,511/呎
-(25年-07月-17日)</t>
+(25年-07月-18日)</t>
         </is>
       </c>
       <c r="L27" s="21" t="inlineStr">
@@ -18606,7 +18606,7 @@
           <t>L | 434呎 (2房)
 $1018万
 $23,459/呎
-(24年-12月-19日)</t>
+(24年-12月-20日)</t>
         </is>
       </c>
     </row>
@@ -18621,7 +18621,7 @@
           <t>A | 512呎 (3房)
 $2150万
 $42,000/呎
-(26年-06月-29日)</t>
+(26年-06月-30日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -18653,7 +18653,7 @@
           <t>E | 358呎 (2房)
 $1432万
 $40,000/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -18661,7 +18661,7 @@
           <t>F | 225呎 (1房)
 $880万
 $39,111/呎
-(26年-02月-25日)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr">
@@ -18669,7 +18669,7 @@
           <t>G | 343呎 (2房)
 $1374万
 $40,058/呎
-(26年-02月-25日)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="I28" s="21" t="inlineStr">
@@ -18677,7 +18677,7 @@
           <t>H | 394呎 (2房)
 $1734万
 $44,000/呎
-(26年-03月-02日)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="J28" s="21" t="inlineStr">
@@ -18685,7 +18685,7 @@
           <t>J | 204呎 (1房)
 $857万
 $42,000/呎
-(26年-03月-11日)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
       <c r="K28" s="21" t="inlineStr">
@@ -18693,7 +18693,7 @@
           <t>K | 340呎 (2房)
 $1360万
 $40,000/呎
-(26年-02月-22日)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="L28" s="21" t="inlineStr">
@@ -18701,7 +18701,7 @@
           <t>L | 397呎 (2房)
 $1628万
 $41,000/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
     </row>
